--- a/sheets/대금율보/검수/뱃노래 (b1_119_1).xlsx
+++ b/sheets/대금율보/검수/뱃노래 (b1_119_1).xlsx
@@ -1879,8 +1879,7 @@
         <is>
           <t xml:space="preserve">南
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -1976,8 +1975,7 @@
         <is>
           <t xml:space="preserve">湳潢
 湳淋
-湳
-‹</t>
+湳</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -1989,8 +1987,7 @@
         <is>
           <t xml:space="preserve">湳潢
 湳淋
-湳
-‹</t>
+湳</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/뱃노래 (b1_119_1).xlsx
+++ b/sheets/대금율보/검수/뱃노래 (b1_119_1).xlsx
@@ -1764,16 +1764,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="86.96" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="97.23" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="97.23" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="97.23" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="97.23" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="97.23" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="97.23" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="97.23" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="97.23" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="97.23" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="97.23" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="97.23" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="97.23" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="97.23" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="97.23" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="97.23" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="97.23" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -2175,6 +2175,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
 </worksheet>
 </file>